--- a/artfynd/A 31739-2026 artfynd.xlsx
+++ b/artfynd/A 31739-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/203035</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Dalaflorans databas</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62593672</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
           <t>Dalaflorans databas</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62544141</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55252445</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
           <t>Dalaflorans databas</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62544136</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,6 +1419,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86894502</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1496,8 +1531,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62511304</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>